--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45509</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45770</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46100</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>44530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45993</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>45798</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44802</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45425</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45699</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45905</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44965</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45588</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>46003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44760</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45553</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46126</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45728</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45422</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44711</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45422</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45712</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44575</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44508</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44648</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44866</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44529</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44507</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44691</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>44887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44824</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44767</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44495</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44715</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44544</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44809</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44473</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44467</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44855</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44563</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44606</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44753</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44550</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44550</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44544</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44482</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45385</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45364</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44803</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>44551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44489</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45590</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45093</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45414</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45585</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44945</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45357</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45008</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45337</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44791</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44894</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45730</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>45212</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45680</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45503</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>45404</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45758</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44558</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45517</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44952</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>44853</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44739</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45355</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45322</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45709</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44553</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44711</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44594</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45054</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45244</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45511</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44986</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45264</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45629</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44923</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44657</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>45698</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>45385</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44896</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45266</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45735</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45735</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44489</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45588</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45159</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45771</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>44867</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>44860</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45235</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44820</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45264</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45498</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44516</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45204</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45190</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44563</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45118</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45730</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45182</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45666</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44923</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45630</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45709</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45187</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44519</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45712</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45637</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45559</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45348</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45352</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45596</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45358</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45011</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45345</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44952</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45884</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45497</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45735</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45607</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45716</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45530</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45888</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45159</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45009</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45113</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>44662</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44735</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45783</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45706</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45889</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45465</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45887</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45320</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45246</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45838</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45818</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44501</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45462</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44588</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45588</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45880</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45720</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45511</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45561</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45790</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44880</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45901</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45365</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45902</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45320</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45905</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44488</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45478</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45852</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45908</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44624</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45910</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45562</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45910</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45910</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45911</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45882</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45910</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45912</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45191</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45614</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45642</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45912</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45682</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45916</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45916</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45917</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>44971</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45916</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45918</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45918</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44578</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44523</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>44926</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45924</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45596</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45324</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45176</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44931</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45931</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44853</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45931</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45931</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45931</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45933</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45933</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45933</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45933</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45933</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45509</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44651</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>45936</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45939</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>44867</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45250</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45939</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45358</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44749</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44578</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45599</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45945</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45945</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45945</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>45616</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46056</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45950</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45235</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45952</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45675</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45204</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46153</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>46153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45959</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45958</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45959</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45958</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45959</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45958</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45174</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45961</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>45961</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>44607</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45964</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45963</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>44977</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45967</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45966</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45545</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45968</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45930</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45973</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45973</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45973</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45973</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45629</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45975</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44497</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45974</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>44931</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45978</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45978</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45978</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45978</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45978</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45978</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45484</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45979</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45337</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45603</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45817</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45981</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>45982</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45316</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45985</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45985</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45985</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44903</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45645</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>46156</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>46156</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>46156</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>46156</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45989</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45989</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45993</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45475</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>44909</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45425</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>46163</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45273</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>46163</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45009</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45161</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>44866</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>44588</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44812</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45520</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45555</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>46008</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45390</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46008</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46009</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>46009</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>46009</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45678</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>46009</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>46009</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>46009</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>46009</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>46009</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>46009</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45624</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45042</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44949</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>44501</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44581</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>45155</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44926</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44729</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>44818</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45135</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45000</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45282</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>44749</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46170</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46170</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45169</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45875</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>46034</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>44748</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46034</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45922</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45581</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45702</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>46174</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>46174</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46174</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46036</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46036</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>46041</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>44776</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46041</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46041</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>46174</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>46041</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45675</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46043</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44971</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44971</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45062</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>46043</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45084</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>46174</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>45603</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45603</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46174</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>46049</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44498</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45509</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44917</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46051</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45366</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45092</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46052</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45447</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45595</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46181</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>44551</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44739</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35997,7 +35997,7 @@
         <v>44615</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36070,7 +36070,7 @@
         <v>45637</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44893</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>44938</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45427</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>44910</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>46065</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>46069</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>46181</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>46181</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>46069</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44606</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>46073</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45574</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>46181</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>46079</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>46079</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>46080</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37399,7 +37399,7 @@
         <v>45250</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>46084</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>46083</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>46083</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>46083</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45515</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>46085</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>46086</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>46188</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>44501</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45579</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45726</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45726</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>46190</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45264</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>46168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>46190</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46190</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>46190</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>45211</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>46098</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>46193</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>46098</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>46195</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>46195</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>46195</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>46195</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>46195</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>46195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46195</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>46104</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>46104</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>45259</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44496</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>45315</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46105</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>45534</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45534</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45672</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>46107</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>46107</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>46107</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>46108</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45317</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>46111</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>44935</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45110</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41011,7 +41011,7 @@
         <v>45611</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45231</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45089</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45709</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>45350</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45488</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45573</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45708</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45635</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>45804</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>44757</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45468</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>45717</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>45594</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45125</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45930</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>44896</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>45818</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42340,7 +42340,7 @@
         <v>45177</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>45364</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45231</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45425</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>46251</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>45251</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>45097</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>44817</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>45100</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>45558</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45706</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>45706</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45770</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46250</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45544</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43440,7 +43440,7 @@
         <v>44551</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>44502</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>46205</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45545</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
         <v>44896</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45545</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>46205</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>45176</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45509</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45702</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45702</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45328</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>44802</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>46254</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>46254</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45110</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45026</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45163</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>44711</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>45349</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45273</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46216</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45112</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>46257</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45607</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45615</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46261</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45495</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45223</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45167</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45488</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>45764</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45418</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>44943</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45222</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45117</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45484</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45100</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>46267</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>44776</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         <v>45189</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>44488</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>46224</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>45764</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45777</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>46230</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45488</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>46230</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45365</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45624</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46232</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46232</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45637</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>46232</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46275</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45784</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>46233</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>46233</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45784</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45639</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>46233</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>46233</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45511</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45678</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         <v>46237</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48537,7 +48537,7 @@
         <v>46237</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>46237</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>46237</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45792</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>45559</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
         <v>46240</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>44873</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45552</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49126,7 +49126,7 @@
         <v>44977</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49199,7 +49199,7 @@
         <v>45481</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45796</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45729</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45799</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45727</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>45740</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>46282</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45735</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>45727</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45728</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45728</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45494</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45735</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>45730</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>45733</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45803</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45804</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45805</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45804</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45810</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45273</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50742,7 +50742,7 @@
         <v>45617</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45198</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50893,7 +50893,7 @@
         <v>45810</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45812</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45812</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45813</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>45811</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>45813</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51331,7 +51331,7 @@
         <v>45198</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51409,7 +51409,7 @@
         <v>45819</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
         <v>45748</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51555,7 +51555,7 @@
         <v>45753</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>45820</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51701,7 +51701,7 @@
         <v>45825</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45825</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45825</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45825</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>45826</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45831</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45831</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>45831</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45831</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45831</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45831</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45796</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45754</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45863</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>44721</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>44712</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>44712</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>44739</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53020,7 +53020,7 @@
         <v>45849</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53093,7 +53093,7 @@
         <v>44908</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53166,7 +53166,7 @@
         <v>45175</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45395</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53312,7 +53312,7 @@
         <v>45395</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>45721</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>44970</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>44812</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45189</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45498</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45665</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
         <v>44712</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53896,7 +53896,7 @@
         <v>45722</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>44958</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45395</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>45518</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54188,7 +54188,7 @@
         <v>45301</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>45873</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>44496</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45873</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45465</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45465</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54626,7 +54626,7 @@
         <v>44469</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54699,7 +54699,7 @@
         <v>45607</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>45611</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54845,7 +54845,7 @@
         <v>44958</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>45465</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>45465</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45465</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55137,7 +55137,7 @@
         <v>45395</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55210,7 +55210,7 @@
         <v>44810</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45077</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>45245</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>45876</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>45876</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55575,7 +55575,7 @@
         <v>45880</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45880</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45882</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45882</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>45882</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45882</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45685</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>44711</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>45673</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>45422</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>45422</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>44711</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>44711</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45422</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>44805</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45422</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45432</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>45720</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45957</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>45985</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>46006</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57327,7 +57327,7 @@
         <v>46041</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>46037</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46041</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46048</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>46051</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46051</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>46052</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57838,7 +57838,7 @@
         <v>46052</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>46062</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46071</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46092</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46098</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>46110</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46110</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58422,7 +58422,7 @@
         <v>46114</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45770</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45509</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>44530</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44802</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44760</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45905</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>44965</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>46003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45425</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45699</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45699</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44711</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45422</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45712</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44575</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44508</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44648</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44866</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44529</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44507</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44691</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>44887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44824</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44767</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44495</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44715</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44544</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44809</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44473</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44467</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44855</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44563</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44606</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44753</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44550</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45322</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45110</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44489</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45385</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44739</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45558</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44551</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45418</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45364</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44812</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44873</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45884</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45465</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45596</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45135</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45559</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45796</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45515</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45607</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45729</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45730</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45494</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45727</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45728</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45728</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45727</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45740</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44923</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44893</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45273</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45235</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44840</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46036</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45706</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45530</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>46036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45838</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44563</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>46041</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>46041</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>46041</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46041</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45545</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>46043</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45561</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44488</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45901</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45900</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45282</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46049</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45092</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45905</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45910</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45908</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45905</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45804</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45910</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45358</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45912</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45912</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45517</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>44615</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45882</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45838</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45916</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45916</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45803</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45918</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>46065</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45555</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44501</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46069</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45924</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45488</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44607</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>46079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46083</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45931</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45931</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45011</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45931</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46083</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>46080</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45805</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45155</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>46084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45617</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>45273</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45931</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45933</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46086</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45933</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45933</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44943</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45933</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45933</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44578</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45498</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45447</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44926</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>46098</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45945</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45945</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45950</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46104</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44749</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45112</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>46107</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45425</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>46107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46108</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45355</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45811</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45958</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45348</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45958</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45959</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45117</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45961</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45961</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45812</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45611</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45588</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45588</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45930</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44867</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45966</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45967</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45812</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44853</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44497</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45026</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45968</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45813</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45971</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45706</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45706</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45971</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44498</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45753</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45974</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45978</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45084</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45978</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45978</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45978</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45978</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45027</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45167</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>44974</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45096</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45982</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45615</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45712</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45113</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45985</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44729</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45989</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45989</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45804</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45645</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45258</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44488</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44662</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45008</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45680</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45545</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46008</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46008</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45475</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>44482</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44926</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45819</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45345</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45637</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>44757</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>46009</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45930</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>44817</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44711</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46009</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>46009</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>46009</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>46009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45716</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45820</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45358</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45880</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45783</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45852</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45273</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45825</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45825</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45509</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45642</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45825</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45414</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45231</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45771</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45534</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45534</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45191</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45264</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45520</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>45425</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44501</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44501</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45831</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44896</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45831</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45831</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46153</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44867</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46056</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>44651</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>44802</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45573</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46156</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46156</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45678</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45349</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44896</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>46156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45222</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46156</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44917</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45337</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45495</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45316</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44971</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44971</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45758</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45250</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>44551</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44553</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45796</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45754</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45922</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44910</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45559</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45104</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45062</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45337</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>46170</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>46170</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45875</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>46174</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>46174</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45863</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>44721</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45545</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>46174</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>46174</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>46174</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>44860</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45482</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45478</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45615</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>46181</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46181</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44489</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46181</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45465</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45465</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45518</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46181</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45666</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45722</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45596</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45365</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45616</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45465</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45611</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45849</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45607</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45395</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45395</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45465</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45465</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45498</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45721</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45077</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44558</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>44739</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45390</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>44958</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45702</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>44496</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44908</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44496</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44469</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>46168</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45189</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45395</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45177</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45726</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45395</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45873</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45175</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44810</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44712</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>46188</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45726</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>44712</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44712</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>44581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45873</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>44958</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45665</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46190</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44812</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45301</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45544</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45484</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45876</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46190</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46195</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45585</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46195</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46193</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45876</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>46195</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45509</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45089</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45054</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45629</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45678</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45880</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45719</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45719</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44578</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45503</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45880</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45882</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45882</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45882</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45882</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45328</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45189</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46205</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>46205</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44606</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45730</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46250</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45169</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44594</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45614</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46251</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45231</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45404</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45404</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45607</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45675</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45708</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>46257</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45244</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45702</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45624</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>46254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>44657</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>45511</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45259</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>46216</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45698</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45211</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>46261</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>44735</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>44776</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44711</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45176</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45581</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45212</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>44903</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45235</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45735</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45159</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45110</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>46266</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>44909</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>44739</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>44820</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45315</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>46224</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>46267</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45317</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45190</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45357</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45264</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45250</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>45163</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45176</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48278,7 +48278,7 @@
         <v>46272</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45366</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>44923</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>46274</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>46230</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45125</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>46230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>46233</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>46233</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>46233</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>46232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>46232</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45264</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>46275</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>46232</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>46237</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>46237</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>46237</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>46237</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>46233</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>44971</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>46286</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>46286</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44588</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>44952</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45764</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45637</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45282</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>44803</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>44915</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46240</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>44502</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>44977</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>46286</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>46290</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51082,7 +51082,7 @@
         <v>45161</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45159</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45590</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45350</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45511</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45182</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45364</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46290</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45595</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46289</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45574</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45462</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45009</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45097</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45008</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45174</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45717</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45009</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>44749</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>44949</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44880</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45097</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44894</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44931</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44931</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45709</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45735</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45223</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45770</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45385</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45675</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45764</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44776</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45100</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45174</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>45191</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45190</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45187</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45352</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>45320</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45509</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>44883</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45709</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45709</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54319,7 +54319,7 @@
         <v>45266</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45468</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45118</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
         <v>44931</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>44624</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45635</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>45562</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>44588</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45682</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45212</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45672</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>45603</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45603</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>44945</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>45484</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45777</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>45784</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45365</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45784</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45624</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45639</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>45637</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45511</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45678</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>45488</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>44711</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45685</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>45673</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45422</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45422</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>44805</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45432</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>45720</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45957</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57327,7 +57327,7 @@
         <v>45985</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>46006</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46037</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>46041</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46048</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>46051</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57838,7 +57838,7 @@
         <v>46052</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>46052</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>46051</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46062</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46062</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46071</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>46092</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46098</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58422,7 +58422,7 @@
         <v>46110</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58495,7 +58495,7 @@
         <v>46110</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>46114</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58641,7 +58641,7 @@
         <v>46290</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>45770</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45509</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>44530</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45400</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44802</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44760</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>45629</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45905</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>44965</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>46003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45425</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45699</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>45699</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44711</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45687</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45422</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45712</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44575</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44508</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44648</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>44866</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>44529</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44802</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44578</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44507</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>44547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44691</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>44887</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44824</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44767</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44495</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44873</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44715</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44544</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44809</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44473</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44467</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44855</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44571</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44606</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44840</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44638</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44563</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44606</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44753</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44606</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44550</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44791</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45322</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45110</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>44489</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45385</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44739</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45427</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45558</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44551</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45418</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45364</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44812</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44873</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45884</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45465</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45596</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45135</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45559</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45497</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45796</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45515</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45607</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45729</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45730</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45494</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45727</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45728</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45728</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45727</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>45740</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44923</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45733</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44893</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45273</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>45799</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45235</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46034</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44840</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46036</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>45706</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45607</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45530</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>46036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>45838</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44563</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>46041</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>46041</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>46041</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>46041</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45545</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>46043</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>46043</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45561</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44488</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45901</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45900</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45282</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46049</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45092</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45905</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>46051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46052</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>46051</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45910</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45908</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45905</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45804</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>45910</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45358</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44935</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45911</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45912</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45912</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         <v>45517</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>44615</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45882</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45838</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45916</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45916</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44938</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>45803</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45918</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>45918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>46065</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45555</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>44501</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46069</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45924</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>44896</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44951</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45488</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44607</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>46079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46083</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45931</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45931</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45011</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45931</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46083</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>46080</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45805</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45810</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>45155</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>46084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45617</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>45273</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45246</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45931</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>45931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45933</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46086</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45933</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45933</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         <v>44943</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>45933</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45933</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45937</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44578</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45939</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45498</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45447</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44926</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>46098</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44748</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46098</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>44986</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>45945</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45945</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45320</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45950</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>46104</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44749</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45112</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>45952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>46107</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46105</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45425</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>46107</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>46108</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45355</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45811</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45958</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45348</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45958</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45959</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>45117</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45961</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45961</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45812</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45964</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45603</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45611</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45588</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45588</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45930</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45938</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44867</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45966</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45967</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45812</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44853</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44497</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>45026</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45968</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45968</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45813</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45971</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45706</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45706</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45971</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44498</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45753</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45974</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45978</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45084</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>45978</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>45978</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45978</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45978</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45000</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45027</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45167</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>44974</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45096</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45981</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45982</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45615</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45712</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45113</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45985</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44729</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45989</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45989</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45804</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45645</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45258</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44488</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45119</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44662</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45888</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45008</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45680</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45545</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46008</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46008</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45475</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>44482</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44926</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45819</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45345</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45637</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>44757</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>46009</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45930</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>44817</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45730</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44711</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46009</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>46009</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>46009</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>46009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46009</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>46009</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>46009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45716</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45820</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45358</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45880</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45783</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45852</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45273</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45825</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45825</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45825</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45509</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45642</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45825</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44840</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45414</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45231</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45771</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45882</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45534</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45534</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45191</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45264</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>45520</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>45425</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44501</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44501</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45831</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44896</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45831</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45831</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46153</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44867</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>46056</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>44651</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>44802</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45573</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45817</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>46156</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>46156</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45678</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45349</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44896</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>46156</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45222</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46156</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44917</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>45337</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45495</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45316</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44971</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44971</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45758</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44974</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45250</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45084</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>44551</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44553</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45796</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45754</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45922</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44910</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45559</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45104</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45062</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45337</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>46170</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>46170</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45875</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>46174</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>46174</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45863</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>44721</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45545</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>46174</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36712,7 +36712,7 @@
         <v>46174</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46174</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>46174</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>44860</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45482</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45478</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45615</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>46181</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46181</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44489</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46181</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45465</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45465</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45518</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>46181</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45666</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45722</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>45596</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45365</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45616</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45465</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45611</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45849</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45607</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45395</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45395</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44970</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45465</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45465</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45498</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45721</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45077</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>44558</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>44739</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45390</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>44958</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45702</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>44496</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44908</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44496</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44469</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45245</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>46168</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45189</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45395</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45177</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45726</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45395</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45873</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45175</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>44810</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44712</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>46188</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45726</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>44712</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44712</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>44581</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45873</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>44958</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45665</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46190</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44812</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45301</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45544</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45484</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45876</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>46190</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46195</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>46195</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45585</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46195</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46193</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46195</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45876</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>46195</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45509</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45089</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45054</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>45629</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45678</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>45880</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45719</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>45719</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43493,7 +43493,7 @@
         <v>44578</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45503</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45880</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45882</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45882</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>45882</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45882</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44004,7 +44004,7 @@
         <v>45328</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45189</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>46205</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>46205</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44606</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45730</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>46250</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45169</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>44594</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45100</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>45614</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46251</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45231</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45404</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45404</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45607</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45675</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45708</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>46257</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45244</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>45702</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45624</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>46254</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>44657</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>45511</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>45259</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46063,7 +46063,7 @@
         <v>46216</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45698</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46209,7 +46209,7 @@
         <v>45211</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
         <v>46261</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>44735</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>44776</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>44711</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46574,7 +46574,7 @@
         <v>45176</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45581</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45212</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>44903</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45235</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>45735</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45159</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45110</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>46266</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>44909</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>44739</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>44820</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>45315</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>46224</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>46267</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45317</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45190</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45357</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45264</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45250</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>45163</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45176</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48278,7 +48278,7 @@
         <v>46272</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45366</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>44923</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>46274</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>46230</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45125</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>46230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>46233</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48872,7 +48872,7 @@
         <v>46233</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48950,7 +48950,7 @@
         <v>46233</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>46232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>46232</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45264</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>46275</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>46232</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49393,7 +49393,7 @@
         <v>46237</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>46237</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>46237</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>46237</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>46233</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49763,7 +49763,7 @@
         <v>44971</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>46286</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>46282</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>46286</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50055,7 +50055,7 @@
         <v>44588</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>44952</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45764</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45637</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45282</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50420,7 +50420,7 @@
         <v>44803</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>44915</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50571,7 +50571,7 @@
         <v>46240</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46268</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>44502</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>44977</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>46286</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>46290</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51082,7 +51082,7 @@
         <v>45161</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45159</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51233,7 +51233,7 @@
         <v>45590</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45350</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45511</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45182</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45364</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46290</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>45595</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46289</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45574</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45462</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45009</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45097</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45008</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45174</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45717</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45009</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>44749</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>44949</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44880</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45097</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44894</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>44931</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44931</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>45709</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45735</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45223</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45770</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45385</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45675</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53365,7 +53365,7 @@
         <v>45764</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>44776</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45100</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45174</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>45191</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45190</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45187</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45352</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>45320</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45509</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>44883</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54168,7 +54168,7 @@
         <v>45709</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>45709</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54319,7 +54319,7 @@
         <v>45266</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54392,7 +54392,7 @@
         <v>45468</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45118</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
         <v>44931</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54611,7 +54611,7 @@
         <v>44624</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54684,7 +54684,7 @@
         <v>45635</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>45562</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>44588</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45682</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45212</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45672</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>45603</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45603</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>44945</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>45484</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45777</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>45784</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45365</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45784</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45624</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55794,7 +55794,7 @@
         <v>45639</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         <v>45637</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45511</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56013,7 +56013,7 @@
         <v>45678</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>45488</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>44711</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>45685</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>45673</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45422</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45422</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>44805</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45432</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>45720</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>45957</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57327,7 +57327,7 @@
         <v>45985</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>46006</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46037</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>46041</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>46048</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57765,7 +57765,7 @@
         <v>46051</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57838,7 +57838,7 @@
         <v>46052</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>46052</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>46051</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>46062</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46062</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46071</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>46092</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>46098</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58422,7 +58422,7 @@
         <v>46110</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58495,7 +58495,7 @@
         <v>46110</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>46114</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58641,7 +58641,7 @@
         <v>46290</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46100</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45509</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45770</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45798</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44530</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46003</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45699</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44760</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45365</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44711</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44473</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44867</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44606</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44638</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44563</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44753</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44606</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44550</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44544</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44945</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45385</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44489</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45414</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45093</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45364</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45585</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44803</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44551</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45357</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45008</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45730</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45174</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44791</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45884</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45680</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45607</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46008</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44840</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>46009</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44840</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>46009</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>46009</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>46009</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45719</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45404</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45404</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>44951</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>45887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45838</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45758</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44853</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45720</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45901</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45545</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44739</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45322</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45355</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>46036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45482</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>46041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>46041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>46041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45792</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>46041</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45908</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45709</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>46043</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45905</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45838</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45911</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44594</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45559</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44873</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45910</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44977</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45481</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44711</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45912</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45796</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45729</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45799</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45727</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46049</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45916</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45917</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45735</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45727</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45728</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45494</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45916</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45730</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45918</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44883</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46051</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>46051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45804</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45054</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45244</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45264</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46052</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>44923</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45924</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45385</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44657</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>44615</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45810</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45273</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45698</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45931</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45931</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45931</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45617</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45931</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45933</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45933</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45933</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44896</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45933</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45266</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45735</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45735</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45588</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>44974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44489</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46069</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45198</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45104</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45810</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45159</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45615</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45945</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45945</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44860</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45235</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>44516</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45812</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45812</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44820</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46079</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45264</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>46083</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46083</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45204</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45813</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>46085</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>46086</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45813</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45958</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45959</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45958</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44896</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45961</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45961</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45964</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44563</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45967</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45118</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45966</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>46098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45968</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45968</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45971</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45198</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45930</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45730</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45607</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45973</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>46104</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>46104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45709</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45975</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45666</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44923</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46105</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45978</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45630</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45187</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44519</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46107</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45819</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46107</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>46107</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45748</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45348</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>46111</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45820</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45637</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45358</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45011</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45559</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45352</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45825</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>45989</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45993</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>44952</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45497</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45735</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45716</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45530</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45831</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45159</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45191</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45831</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45211</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45113</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44735</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45804</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45465</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45320</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45246</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44501</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44894</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45462</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44588</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45588</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45511</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44880</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45167</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45365</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45345</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45155</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45320</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45478</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44624</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45562</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45614</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45682</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44662</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44971</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45783</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>44974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44578</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44523</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44926</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45880</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45796</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45754</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45596</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45324</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44931</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44853</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>44488</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45852</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45509</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45863</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>44651</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45882</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>44721</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45191</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>44867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45358</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44749</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>44578</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>44712</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44712</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44739</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45849</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45599</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45008</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45175</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45395</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45395</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45721</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45616</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44970</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45498</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44712</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45722</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44958</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45395</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45518</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45301</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45235</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45873</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45675</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44496</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45873</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45204</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45084</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45465</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45465</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45611</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46056</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>44958</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45465</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45465</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45465</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45395</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44810</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45077</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45245</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>46153</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>46153</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44607</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>44977</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45817</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45545</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45678</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>46156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>46156</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>46156</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>46156</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45629</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>46163</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44497</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44931</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>46163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45876</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45484</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45337</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45603</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45876</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45316</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>44903</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45880</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45645</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>46170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>46170</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45880</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45875</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45922</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46174</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46174</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46174</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45882</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>46174</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46174</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45882</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45475</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44909</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46181</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46181</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45425</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45273</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>46181</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>46181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45009</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45161</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46181</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44866</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>44588</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>46188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45726</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45726</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>44812</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>46190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45520</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46168</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>46190</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46190</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46190</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46193</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45555</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45390</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46195</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46195</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>46195</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45624</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45042</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>46195</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44949</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>44501</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>44581</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45155</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>44926</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>44729</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44818</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45135</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45000</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45282</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>44749</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45169</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>44748</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45581</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45702</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>46205</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>46205</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44776</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45096</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45675</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44971</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44971</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45062</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45084</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45603</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45603</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46216</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46257</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>44498</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45509</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>44917</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>46261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>44915</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45366</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45447</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45595</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>44551</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>44739</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45637</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44893</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>44938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45427</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>44910</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45282</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>46224</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>44606</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45574</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>46230</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45250</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>46230</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>46232</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>46232</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45515</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46232</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>46275</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>46233</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>46233</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46233</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>46237</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45190</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>44501</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45579</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45264</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45211</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46282</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45259</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>44496</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>45315</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45534</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45534</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46286</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45672</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46286</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46287</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45317</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>44935</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45110</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45611</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45089</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45709</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45350</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45488</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>46289</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45573</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45708</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45635</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>46290</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46250</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>44757</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45468</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45717</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>45594</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45125</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>44896</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45177</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>46251</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45364</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45231</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45425</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45251</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45097</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>44817</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45100</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45558</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>45706</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45706</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45770</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>45544</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45831</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>46174</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>46254</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>44551</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46254</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>46297</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>44502</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>45545</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>44896</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45545</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45176</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45509</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45702</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>45702</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45328</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>44802</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45110</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>45026</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45163</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>44711</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45349</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45273</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45607</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45615</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>45495</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>45223</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54210,7 +54210,7 @@
         <v>45167</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45488</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45764</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45418</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54502,7 +54502,7 @@
         <v>44943</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54575,7 +54575,7 @@
         <v>45222</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54648,7 +54648,7 @@
         <v>45117</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45484</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45100</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>44776</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45189</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44488</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45764</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45777</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45488</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>45365</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45624</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>45637</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45784</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>45784</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45639</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45685</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44711</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>45673</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>44711</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44711</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45422</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45422</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45422</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>44805</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45432</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45720</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45957</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45985</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>46006</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46041</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46037</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46041</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>46048</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>46051</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>46051</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46052</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>46052</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46062</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46062</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>46071</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>46092</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46098</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46110</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>46110</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>46114</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46290</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46100</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45509</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45770</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45798</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44530</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45400</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45629</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46003</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45728</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45699</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>44965</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45588</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44760</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45365</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44711</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44473</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44867</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44606</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44638</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44563</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44753</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44606</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44550</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44544</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44482</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44945</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45385</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44489</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45414</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45093</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45364</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45585</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44803</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44551</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45357</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45008</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45337</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45730</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45174</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44791</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45678</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45884</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45680</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>46009</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45607</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>46008</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44840</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>46009</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>46009</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44840</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>46009</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>46009</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>46009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>46009</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>46009</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>45719</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>45404</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45404</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>44951</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>45887</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45838</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45758</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44952</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44853</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44558</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45720</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45517</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45561</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>45790</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45901</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45545</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44739</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45322</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45355</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>46036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45482</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>46041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45905</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>46041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>46041</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45792</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>46041</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45908</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45709</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>46043</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45905</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>45910</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>45838</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45911</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44594</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45559</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44873</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>45882</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45910</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>44977</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45481</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44711</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45912</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>44931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45796</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45729</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45799</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45727</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>46049</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45740</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45916</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>45511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45916</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45917</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45735</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45727</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45728</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45728</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45494</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45735</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45916</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45730</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45733</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45803</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45918</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44883</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46051</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>46051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45804</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45054</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45244</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>45264</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>46052</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>44923</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45924</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45385</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44657</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>44615</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45810</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>45273</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>45698</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45931</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45931</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45931</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45617</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45931</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45931</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45933</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45933</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45933</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44896</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45933</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45266</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45735</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45735</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45588</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>44974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44489</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>46069</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45198</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45104</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45810</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45159</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45771</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45615</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45945</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45945</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>44860</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45235</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44867</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>44516</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45812</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45812</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44820</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>46079</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45952</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45264</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>46083</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46083</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45204</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45813</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>46085</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>46086</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45811</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45959</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45813</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45958</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45959</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45958</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44896</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45190</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45961</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45961</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45964</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44563</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45963</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45967</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45118</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45966</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>46098</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45968</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45968</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45971</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45971</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45938</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45198</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45930</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45730</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45607</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45973</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>46104</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>46104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45974</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45709</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45975</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45666</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44923</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>46105</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45978</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45978</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45630</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45187</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44519</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45981</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>46107</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45819</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46107</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>46107</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>46108</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45748</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45753</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45348</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>46111</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45820</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45985</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45985</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45637</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45358</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45011</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45559</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>45352</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45825</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>45989</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45993</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>44952</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>45497</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>45735</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45716</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45530</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45831</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45831</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45159</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45191</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45831</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>45009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45211</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45113</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44735</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45804</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45465</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45320</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45246</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>44501</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44894</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45462</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44588</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45588</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45818</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45511</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>45027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>44880</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45167</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45365</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45345</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45155</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45320</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45478</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44624</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45562</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45614</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45682</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44662</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44971</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>45783</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>44974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44578</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32362,7 +32362,7 @@
         <v>45818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44523</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44926</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45880</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45796</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>45754</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32873,7 +32873,7 @@
         <v>45596</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45324</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44931</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44853</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>44488</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45852</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45509</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45863</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>44651</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45882</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>44721</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45097</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45191</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>44867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45358</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45642</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44749</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>44578</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>44712</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>44712</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44739</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45849</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45599</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45008</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45175</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45395</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45395</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45721</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45616</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44970</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45498</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>44712</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45722</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>44958</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45395</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45518</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35964,7 +35964,7 @@
         <v>45301</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45235</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45873</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45675</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44496</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>45873</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45204</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45084</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45465</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45465</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>45607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45611</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46056</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>44958</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -36996,7 +36996,7 @@
         <v>45465</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45465</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45465</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45395</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>44810</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45077</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45245</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45174</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>46153</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>46153</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37736,7 +37736,7 @@
         <v>44607</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>44977</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45817</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>45545</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45678</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>46156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>46156</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>46156</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>46156</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45629</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>46163</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44497</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>44931</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>46163</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>45876</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45484</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45337</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45603</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45876</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45316</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>44903</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45880</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45645</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39440,7 +39440,7 @@
         <v>46170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>46170</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45880</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>45875</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45922</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46174</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46174</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46174</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45882</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>46174</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40263,7 +40263,7 @@
         <v>46174</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45882</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45475</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44909</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46181</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>46181</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45425</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45273</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>46181</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>46181</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>45009</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45161</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46181</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>44866</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>44588</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>46188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45726</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45726</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>44812</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>46190</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45520</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>46168</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>46190</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46190</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>46190</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>46193</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45555</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45390</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>46195</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>46195</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46195</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>46195</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45624</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43004,7 +43004,7 @@
         <v>45042</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>46195</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44949</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>44501</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>44581</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45155</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>44926</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>44729</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>44818</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45135</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45000</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45282</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>44749</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45169</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>44748</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45581</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45702</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>46205</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>46205</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44776</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45096</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45675</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44971</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>44971</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45062</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45084</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45603</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45603</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46216</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46257</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>44498</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45287,7 +45287,7 @@
         <v>45509</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>44917</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>46261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>44915</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45366</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45447</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45595</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>44551</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>44739</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45637</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>44893</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>44938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45427</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>44910</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45282</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>46224</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>46266</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>44606</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45574</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>46230</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45250</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>46230</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>46232</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>46232</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45515</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>46232</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>46274</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>46275</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>46233</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>46233</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46233</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>46237</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46237</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45190</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>44501</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45579</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45264</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>45211</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46282</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45259</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48758,7 +48758,7 @@
         <v>44496</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48831,7 +48831,7 @@
         <v>45315</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48904,7 +48904,7 @@
         <v>45534</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45534</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46286</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45672</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>46286</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>46287</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>46268</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45317</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>44935</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45110</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45611</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45089</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45709</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>46240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45350</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45488</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>46289</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>45573</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45708</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45635</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>46290</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>46250</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>44757</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45468</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45717</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50968,7 +50968,7 @@
         <v>45594</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45125</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51114,7 +51114,7 @@
         <v>44896</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45177</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>46251</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45364</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45231</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45425</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45251</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45097</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>44817</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45100</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45558</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>45706</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45706</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45770</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>45544</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45831</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>46174</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>46254</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>44551</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46254</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>46297</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>44502</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>45545</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52803,7 +52803,7 @@
         <v>44896</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52876,7 +52876,7 @@
         <v>45545</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45176</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45509</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45702</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>45702</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45328</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>44802</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>45110</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>45026</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45163</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>44711</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45349</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45273</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>45112</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45607</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45615</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>45495</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>45223</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54210,7 +54210,7 @@
         <v>45167</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45488</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>45764</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45418</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54502,7 +54502,7 @@
         <v>44943</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54575,7 +54575,7 @@
         <v>45222</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54648,7 +54648,7 @@
         <v>45117</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45484</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>45100</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>44776</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45189</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44488</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45764</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45777</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45488</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>45365</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45624</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>45637</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45784</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>45784</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45639</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45685</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44711</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>45673</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>44711</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44711</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45422</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45422</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45422</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>44805</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45432</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45720</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45957</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45985</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>46006</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46041</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>46037</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>46041</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>46048</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>46051</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>46051</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46052</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>46052</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46062</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46062</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>46071</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>46092</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46098</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46110</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>46110</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>46114</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46290</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45509</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45798</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45993</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>44760</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45365</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45699</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45588</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45728</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44965</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44742</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>46126</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46003</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>44748</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44711</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45422</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44495</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44715</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44867</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44563</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44544</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44558</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44855</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44550</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44571</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44867</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45110</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45211</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44651</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44802</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45349</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45223</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45322</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45770</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45337</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45495</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45385</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45675</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45316</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45427</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45764</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45093</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44971</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45758</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45418</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44489</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45187</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44739</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45320</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45084</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45364</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45509</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44551</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44883</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45709</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45266</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45468</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45118</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45465</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44931</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45135</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45887</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44840</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45559</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45062</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45706</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45497</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44624</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45515</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44923</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45838</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45720</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44893</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45273</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44519</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45235</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>44853</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>45561</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45562</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45902</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44523</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45530</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45900</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44588</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45790</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45488</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45682</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45545</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45672</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44860</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45167</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45603</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45603</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44563</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45482</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45545</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45905</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45478</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45615</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45484</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45910</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45905</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>44489</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45910</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45777</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45912</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45282</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45666</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45365</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45882</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45838</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45916</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45092</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45365</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45624</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>44558</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>44551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45390</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45639</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45918</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45637</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45702</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45358</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45917</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44496</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44938</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45511</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45678</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44581</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45555</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45924</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44501</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45544</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45484</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45585</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45509</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45089</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45204</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45054</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45204</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45629</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45678</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44951</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45488</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>44873</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44977</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45719</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44578</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45503</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45011</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45630</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45481</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45792</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45246</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45796</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45552</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45729</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45730</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45494</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45727</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45728</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45728</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45931</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45931</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45727</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45740</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45735</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45931</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45933</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45799</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45328</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45189</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45933</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44578</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45804</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45804</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45933</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45803</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45498</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45447</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>44926</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>44606</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44748</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45730</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45805</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45810</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45169</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45320</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44594</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45100</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45614</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45617</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45273</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45599</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45198</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45810</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45231</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45735</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44749</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45404</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45404</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45607</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45594</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45425</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45811</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45812</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45945</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45813</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45813</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45945</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45675</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45945</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45708</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45355</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45753</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45748</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45348</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45198</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45950</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45819</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45579</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45244</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45702</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45117</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45820</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45624</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45629</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45042</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45825</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45603</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45825</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45611</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45588</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45588</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>44867</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>44853</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>44497</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44657</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45952</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45026</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45511</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45259</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45831</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45706</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45706</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45831</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45958</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45958</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45958</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44498</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45959</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45959</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45959</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45959</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45698</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45211</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45961</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45961</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45000</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45027</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45963</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44735</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45964</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45167</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>44776</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>44974</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>44711</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45096</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45581</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45212</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45930</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45938</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45615</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45712</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45966</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45968</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45968</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45113</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45971</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44903</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45235</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45735</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45159</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45973</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>44729</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45973</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45973</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45110</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44909</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44739</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44820</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45974</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45315</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45645</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45975</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45978</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45978</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45978</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45317</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45190</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>45796</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45754</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45357</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45119</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45978</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45264</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45863</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45250</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44721</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45978</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45176</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45465</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45465</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45518</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>45680</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45722</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>45366</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>45545</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45465</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45611</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45849</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45395</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45395</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45475</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>44970</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>44482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45465</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45465</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45498</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45721</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>44926</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45077</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>44923</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44739</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44757</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44958</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>44496</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44908</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45395</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45395</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45873</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44712</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44712</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44712</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44817</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45730</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44711</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45873</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44958</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45665</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>44812</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45301</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45716</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45876</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45125</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44894</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45358</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45880</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45981</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45880</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45273</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45882</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45155</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>45264</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45882</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45982</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46098</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46098</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45509</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44840</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46104</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46104</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45414</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45231</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45771</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45985</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>44971</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>46107</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46107</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>46105</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45251</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46107</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45534</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45534</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46111</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45264</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45989</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45520</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45989</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45425</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44501</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44501</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44588</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45993</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>44952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45764</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45637</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>44803</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44915</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44502</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44977</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46008</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>46008</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45818</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45161</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45159</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45590</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>46009</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45350</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>46009</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45511</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45804</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>46009</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>46009</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>46009</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46009</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46009</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>46009</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>46009</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>46009</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45182</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45364</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45595</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45574</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45258</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>45462</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>44488</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44662</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45888</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45009</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>45818</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46034</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45345</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46034</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>46036</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45937</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45930</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>46036</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45008</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45174</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45717</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>46041</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>46041</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46041</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>46041</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46043</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45880</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45783</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45009</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45852</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>46043</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>44749</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>44949</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45642</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>44880</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>46049</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46051</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>46052</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>46051</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44615</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45882</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45191</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>46065</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46069</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46153</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46153</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>46073</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>46056</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>46079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46079</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45817</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46083</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>46083</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>46080</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>46156</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46156</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45678</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46084</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>46156</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>46085</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>46086</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>46156</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>46163</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>46163</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45922</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46170</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46170</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>46174</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46174</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46174</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46174</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46181</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>46181</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>46181</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>46181</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>46181</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46168</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>45726</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>46188</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45726</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46190</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46190</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>46195</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>46195</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>46193</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>46195</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46195</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>46205</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>46205</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>46216</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>46266</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46224</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46267</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>46267</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46272</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>46230</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46230</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>46233</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>46233</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>46233</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>46232</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>46232</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>46275</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>46232</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>46237</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>46237</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>46237</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>46237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>46233</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>46286</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>46282</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>46240</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46268</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>46287</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>46286</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>46290</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54210,7 +54210,7 @@
         <v>46290</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>46289</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>46250</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>46251</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45733</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45735</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45637</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>46300</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>46257</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>46009</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45831</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>46174</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>46174</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55247,7 +55247,7 @@
         <v>46254</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>46300</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>46254</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>46297</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>46301</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>46301</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46301</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46261</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46303</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>44711</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>44711</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>45685</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>45673</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45422</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44805</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>45422</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45432</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>45720</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45957</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>45985</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>46006</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>46037</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>46041</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46048</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>46051</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46052</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46052</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46062</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46071</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46092</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46098</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46110</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46110</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>46114</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46290</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45770</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45509</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>46100</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44530</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45232</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45798</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45400</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45993</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>44760</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45365</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45699</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45588</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45728</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>44965</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>45699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>44742</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>46126</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46003</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>44748</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44711</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45422</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44495</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44845</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>44715</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>44867</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44563</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44544</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44594</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44558</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44855</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44840</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45385</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44550</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44571</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45702</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44867</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45110</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45211</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44651</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44802</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45349</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45223</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45322</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>44917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45770</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45337</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45495</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45385</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45675</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>44818</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45316</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45427</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>44952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45764</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45093</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44971</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>44971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>44776</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45758</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45418</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44489</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45191</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45187</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>44739</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45320</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45084</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45364</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45509</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>44551</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>45884</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>44883</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45709</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45266</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45468</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45118</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45465</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44931</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45135</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45887</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44840</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45559</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45062</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45706</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45607</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>45497</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44624</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45635</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45515</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>45607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45889</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44923</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45838</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45720</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44893</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45273</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44519</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45235</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>44853</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>45561</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45562</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45902</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>44523</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45530</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45900</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44588</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45790</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45488</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45682</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45545</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45672</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44860</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45167</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45603</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45603</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44563</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>44896</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45482</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44945</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45545</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45905</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>45478</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45615</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45484</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45910</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45908</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45905</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>44489</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45910</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45910</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45777</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>45912</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45912</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45282</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45666</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>45365</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45882</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45838</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45916</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45092</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45916</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45784</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45365</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45624</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>44558</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>44551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45390</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45639</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45918</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45637</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45702</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45358</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45917</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45517</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44496</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>45918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>44938</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>45177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45511</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>45678</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45488</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44581</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45555</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45924</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44501</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45544</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45484</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>44896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45585</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45509</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45089</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45204</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45054</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45204</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45629</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45678</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44951</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45488</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>44873</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44977</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45719</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45719</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44578</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45503</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45011</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45630</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45481</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45155</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45792</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45246</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45796</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>45552</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45729</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45730</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45494</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45727</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45728</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45931</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45728</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45931</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45931</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45727</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45740</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45735</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45931</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45933</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44943</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45799</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45328</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45189</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45933</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44578</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45804</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45804</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45933</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45933</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45803</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45498</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45447</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>44926</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>44606</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44748</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45730</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45805</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45810</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45169</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45320</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44594</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45100</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45614</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45617</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45273</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45599</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45198</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45810</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45231</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45735</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>44749</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45404</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45404</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45939</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45607</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45594</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45425</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45811</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45812</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45945</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45813</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45813</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45945</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45675</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45945</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45708</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45355</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45753</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45748</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45348</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45198</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45950</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45819</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45579</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45244</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45702</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45117</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45820</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45624</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45629</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45042</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45825</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45603</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45825</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45611</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45588</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45588</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>44867</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>44853</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>44497</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>44657</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45952</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45026</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45511</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45259</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45831</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45706</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45706</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45831</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45958</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45958</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45958</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44498</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45959</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45959</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45959</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45959</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45698</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45211</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45961</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45084</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45961</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45000</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45027</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45963</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44735</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45964</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45167</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>44776</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>44974</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>44711</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45176</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45096</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45581</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45212</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45930</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45938</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45615</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45712</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45966</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45163</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45968</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45968</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45113</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45971</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44903</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45235</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45735</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45159</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45971</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45973</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>44729</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45973</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45973</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45973</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45973</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45110</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44909</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44739</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>44820</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45974</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45315</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45645</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>45975</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45978</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45978</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45978</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45317</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>45190</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>45796</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45754</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45357</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45119</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45978</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45264</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45863</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45250</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44721</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45978</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45978</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45978</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45176</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45465</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45465</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45518</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36213,7 +36213,7 @@
         <v>45680</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36286,7 +36286,7 @@
         <v>45722</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>45366</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>45545</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45465</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45611</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45849</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45395</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45395</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45475</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>44970</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>44482</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45465</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45465</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45498</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45721</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>44926</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45077</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>44923</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44739</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44757</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44958</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>44496</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>44908</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45245</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>45189</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45395</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45395</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45873</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44810</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44712</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>44712</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>44712</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>44817</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45730</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>44711</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>45873</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44958</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45665</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>44812</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45301</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45716</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45876</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45125</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44894</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45358</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45880</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45981</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>45880</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45882</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45273</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45882</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45155</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         <v>45264</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45882</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45982</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>46098</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>46098</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45509</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>44840</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46104</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46104</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>45414</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45231</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45771</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45985</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45985</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>44971</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>46107</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>46107</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>46105</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45251</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46107</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45534</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45534</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>46111</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45264</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42297,7 +42297,7 @@
         <v>45989</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45520</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42448,7 +42448,7 @@
         <v>45989</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42521,7 +42521,7 @@
         <v>45425</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44501</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44501</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44588</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45993</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>44952</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45764</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45637</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>44803</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44915</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>44502</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>44977</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46008</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>46008</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45818</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45161</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45159</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45590</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>46009</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45350</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>46009</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>45511</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45804</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>46009</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>46009</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>46009</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>46009</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>46009</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>46009</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>46009</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>46009</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45182</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>45364</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45595</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>45574</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45258</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>45462</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>44488</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44662</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>45888</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45009</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>45818</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46034</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45345</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46034</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>46036</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45937</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>45930</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>46036</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45008</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45174</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45717</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>46041</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>46041</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46041</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>46041</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46043</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45880</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45783</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45009</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45852</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>46043</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>44749</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>44949</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45642</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>44880</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>46049</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46051</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>46052</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>46051</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44615</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45882</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45191</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>46065</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46069</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46069</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46153</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46153</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>46073</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>46056</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>46079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>46079</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45817</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46083</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>46083</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>46080</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>46156</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>46156</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45678</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>46084</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>46156</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         <v>46085</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>46086</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49536,7 +49536,7 @@
         <v>46156</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>46163</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>46163</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49760,7 +49760,7 @@
         <v>45922</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>46170</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>46170</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>46174</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46174</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>46174</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>46174</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>46181</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>46181</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>46181</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>46181</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>46181</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46168</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>45726</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>46188</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45726</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>46190</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>46190</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51265,7 +51265,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>46195</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>46195</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>46193</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>46195</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>46195</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>46195</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>46205</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>46205</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>46216</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>46266</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>46224</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46267</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>46267</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>46272</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>46230</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>46230</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52730,7 +52730,7 @@
         <v>46233</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>46233</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52886,7 +52886,7 @@
         <v>46233</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52964,7 +52964,7 @@
         <v>46232</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53037,7 +53037,7 @@
         <v>46232</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>46275</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>46232</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>46237</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>46237</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53402,7 +53402,7 @@
         <v>46237</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53475,7 +53475,7 @@
         <v>46237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>46233</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>46286</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>46282</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53845,7 +53845,7 @@
         <v>46240</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>46268</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>46287</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>46286</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>46290</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54210,7 +54210,7 @@
         <v>46290</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>46289</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54356,7 +54356,7 @@
         <v>46250</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>46251</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45733</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>45735</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45637</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45978</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>46300</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>46257</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>46009</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>45831</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>46174</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>46174</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55247,7 +55247,7 @@
         <v>46254</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>46300</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>46254</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>46297</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>46301</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>46301</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>46301</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>46261</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>46303</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>44711</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>44711</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>44711</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>45685</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>45673</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>45422</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44805</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>45422</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45432</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>45720</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45957</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>45985</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>46006</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>46037</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>46041</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46041</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46048</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>46051</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46052</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46052</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46062</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46062</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46071</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46092</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46098</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46110</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46110</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>46114</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46290</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45509</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45770</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45232</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45993</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45699</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44965</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>46003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44760</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45553</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44742</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45699</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45728</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44711</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44691</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44563</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44753</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44550</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44544</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44945</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45385</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45212</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>45364</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44803</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44551</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44489</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45414</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45212</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45337</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44791</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45730</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45174</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45680</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45404</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45404</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44951</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45758</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44853</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45355</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45482</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45545</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45322</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44594</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45709</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44883</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45054</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45629</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45264</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44923</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44657</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45698</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45385</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45104</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45735</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45588</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45159</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45771</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44860</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45235</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44867</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45264</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44516</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45190</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>44563</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45118</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45607</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45730</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45666</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44923</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45709</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45348</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45596</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45882</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45345</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45358</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45011</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45884</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45712</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45352</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44840</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45888</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44662</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44952</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45497</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45735</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>45889</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>45716</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45880</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45530</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45159</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45211</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45884</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44735</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45900</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45561</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45465</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45852</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45901</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45882</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>45191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45320</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45642</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45905</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>44501</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44894</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45462</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44588</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45588</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45910</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45910</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45912</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45511</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45027</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45155</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45320</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44624</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45562</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45682</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>46056</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45931</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45931</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45931</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45931</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45931</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45933</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45933</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45933</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45933</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45933</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46153</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46153</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44578</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45937</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44523</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45939</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44926</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45945</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45945</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45176</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44853</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45509</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44651</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45817</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45678</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45097</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44867</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45959</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45250</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>46156</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>46156</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46156</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46156</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45358</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45961</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44578</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45964</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45599</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45963</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45968</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45968</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45971</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45971</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45938</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45930</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45235</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45973</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45675</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45975</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45084</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45978</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45174</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44607</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44977</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45545</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45989</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45989</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45629</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44497</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>44931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45337</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45603</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>46170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45875</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45316</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44903</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45922</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45645</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46009</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>46008</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46008</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46009</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46009</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46009</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46174</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>46009</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46174</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46009</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46009</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>46009</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45475</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>46174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>44909</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45425</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45161</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44866</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44588</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46034</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46036</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46036</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46181</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46181</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>46041</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46041</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46041</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46041</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46043</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46043</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44812</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45520</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45555</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>46181</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45390</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46051</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45678</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46051</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46052</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45624</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45042</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44949</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44501</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46181</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44581</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44615</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44926</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>44729</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46065</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44818</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45135</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46069</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45000</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>46069</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46188</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46073</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45282</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44749</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44748</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46079</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>46079</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>46080</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46084</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45581</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46083</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>46083</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45702</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46085</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46086</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45726</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>45726</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44776</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46190</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>46168</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45096</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>46190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45675</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46190</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44971</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44971</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46193</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45062</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45084</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45603</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45603</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46098</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46195</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>44498</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45509</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46195</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46104</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>46195</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>46195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44917</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44915</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45366</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45092</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>46105</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45447</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45595</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44551</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44739</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>46107</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46107</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>46107</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45637</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46108</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>44893</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44938</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45427</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44910</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45282</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44606</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45574</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45804</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45250</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45515</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45930</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45190</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45818</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44501</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45579</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>45264</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46205</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45211</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45259</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>44496</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45315</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45534</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45534</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45672</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46216</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45317</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44935</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45110</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45611</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45089</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46224</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45709</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45350</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45488</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46230</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46272</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45573</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45708</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46230</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46232</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46232</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46232</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45635</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46274</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46275</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>46233</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>46233</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46233</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46233</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44757</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45468</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45717</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45594</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45125</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44896</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46237</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46237</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>46237</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45364</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45231</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45425</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45097</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>44817</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46282</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45100</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45558</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45706</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45706</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45770</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45544</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44551</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>46286</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>44502</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45545</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44896</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45545</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46286</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46287</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45176</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45509</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45702</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45702</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45328</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>46240</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>44802</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45110</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46289</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45026</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45163</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>44711</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45349</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45273</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45607</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>46290</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>46290</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>46250</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45615</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45495</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45167</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45488</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45764</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45418</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>46251</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>44943</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45222</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45117</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45484</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45100</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44776</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45189</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>44488</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45764</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45831</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46174</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46254</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>46254</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46297</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45978</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45735</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45733</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>46301</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46257</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46301</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45777</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>46301</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45488</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45365</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45624</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45637</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>46174</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>46300</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>46009</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45784</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>46301</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45784</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45639</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45511</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45678</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>46303</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45559</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>44873</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45552</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>44977</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>46261</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45481</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45796</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45729</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45799</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45727</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45740</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45735</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45727</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45728</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45728</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45494</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45730</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>45803</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46308</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45804</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45805</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45804</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>46300</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45810</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45273</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>45617</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>45198</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>46308</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>45810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46268</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45812</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>45812</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45813</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46310</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>45811</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51743,7 +51743,7 @@
         <v>45813</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>46267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>46267</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45198</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45819</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45748</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45753</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45820</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>46310</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>45825</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>45825</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45825</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45825</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45831</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>45831</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45831</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45831</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45796</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45754</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45863</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>44721</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>44712</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>44712</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>44739</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>45849</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>44908</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>45175</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45395</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45395</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>45721</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>44970</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>44812</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45189</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45498</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>45665</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54308,7 +54308,7 @@
         <v>44712</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45722</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>44958</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45395</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45518</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>45301</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45873</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44496</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45873</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45465</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45465</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45607</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45611</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>44958</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45465</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45465</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45465</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45395</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44810</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45077</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45245</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45876</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45876</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45880</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45880</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>45685</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>45673</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>44711</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>44711</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44711</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>44711</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>44805</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45422</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>45432</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>45720</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45957</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>45985</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46006</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46041</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>46037</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46041</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46051</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46052</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46052</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46062</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46062</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46071</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>46098</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46110</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46110</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>46114</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>46290</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>45509</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45770</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45232</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45400</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>45993</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45798</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45425</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45699</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>45629</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44965</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>46003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44748</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45588</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44760</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45553</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45365</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44742</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45699</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45728</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44711</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44547</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44691</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44563</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44753</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44550</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44544</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44945</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45385</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>45212</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>45364</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44803</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44551</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44489</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45590</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>45585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45414</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45212</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45357</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45337</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44791</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>45730</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44894</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>45174</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45680</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45211</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45503</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45404</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45404</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>44951</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44558</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45758</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44853</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45355</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44739</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45482</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45545</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45322</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44711</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44594</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45709</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44553</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44883</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45054</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45244</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45629</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45264</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44923</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>44657</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45698</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45385</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45104</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45735</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44489</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45588</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45159</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45771</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>44860</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45235</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44867</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45264</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45498</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>44516</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45204</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45190</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>44563</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45118</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45607</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>45730</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45666</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44923</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>45709</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>45348</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>44519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45596</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45882</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>45345</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45358</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45011</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45884</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45712</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>45559</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>45352</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44840</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45888</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44662</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45783</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44952</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
         <v>45497</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15301,7 +15301,7 @@
         <v>45735</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>45889</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>45716</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>45880</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>45530</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>45838</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45159</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45211</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45113</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45884</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44735</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45900</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45561</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45465</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45852</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45901</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45882</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>45191</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45320</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45642</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45905</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>44501</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>44894</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45462</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44588</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45588</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45910</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>45882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45910</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45910</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45912</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45511</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45027</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45365</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45155</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45320</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45478</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44624</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45562</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45682</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>46056</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45931</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45931</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45931</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45931</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45931</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45931</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>45933</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45933</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45933</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45933</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45933</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46153</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46153</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44578</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45937</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44523</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45939</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44926</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45596</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45945</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45945</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45176</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44853</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45950</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45509</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45952</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44651</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45817</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45678</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45097</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>44867</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>45959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45959</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45250</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>46156</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>46156</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46156</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46156</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45358</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45961</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44578</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45964</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45599</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45008</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45963</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45967</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45966</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45968</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45968</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45971</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45971</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45938</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45930</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45235</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45973</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45675</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45974</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45975</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46163</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45084</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45978</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45174</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45981</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>44607</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45982</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45985</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44977</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45545</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45989</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45989</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45629</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44497</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>44931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45484</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45337</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45603</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>46170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45875</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45316</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44903</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45922</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45645</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46009</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>46008</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46008</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46009</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46009</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46009</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46174</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>46009</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46174</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46009</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46009</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>46009</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46009</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45475</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>46174</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>44909</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45425</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45273</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45161</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44866</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46034</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44588</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46034</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46036</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46036</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46181</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46181</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>46041</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46041</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46041</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>46041</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>46043</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46043</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44812</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45520</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45555</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>46181</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46049</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45390</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>46181</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>46051</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45678</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>46051</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46052</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>45624</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45042</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44949</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44501</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46181</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44581</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45155</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44615</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>44926</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>44729</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46065</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44818</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45135</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>46069</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45000</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>46069</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>46188</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46073</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45282</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44749</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>44748</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46079</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>46079</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>46080</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46084</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45581</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46083</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>46083</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45702</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>46085</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46086</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45726</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>45726</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44776</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>46190</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>46168</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45096</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>46190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45675</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>46190</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>44971</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44971</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>46193</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45062</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45084</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45603</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45603</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46098</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>46098</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46195</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>44498</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45509</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46195</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46195</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46195</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46104</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>46195</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>46195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44917</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44915</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45366</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45092</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>46105</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45447</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45595</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44551</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44739</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>46107</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>46107</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>46107</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45637</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>46108</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>44893</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>44938</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>45427</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44910</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45282</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44606</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45574</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45804</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45250</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45515</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>45930</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>45190</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45818</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44501</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45579</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>45264</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>46205</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>46205</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45211</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45259</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>44496</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45315</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45534</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45534</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>45672</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46216</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>45317</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44935</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45110</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45611</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45089</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46224</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45709</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45350</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45488</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46230</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46272</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>45573</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45708</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46230</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46232</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46232</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46232</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45635</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>46274</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46275</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>46233</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>46233</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>46233</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46233</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44757</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>45468</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45717</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45594</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45125</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44896</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46237</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46237</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>46237</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>45364</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45231</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45425</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45097</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>44817</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46282</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45100</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45558</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45706</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>45706</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>45770</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45544</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44551</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>46286</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>44502</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45545</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>44896</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>45545</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46286</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>46287</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44144,7 +44144,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45176</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45509</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45702</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45702</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45328</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>46240</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>44802</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45110</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>46289</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45026</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45163</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>44711</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45349</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45273</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45607</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>46290</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>46290</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>46250</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45615</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45495</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45223</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45167</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45488</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45764</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45418</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>46251</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>44943</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45222</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45117</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45484</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45100</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44776</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45189</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>44488</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45764</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45831</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46174</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46254</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>46254</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46297</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45978</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45735</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45733</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>46301</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46257</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46301</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45777</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>46301</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45488</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45365</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45624</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45637</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>46174</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>46300</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>46009</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45784</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>46301</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45784</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45639</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45511</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45678</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46303</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>46303</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45792</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45559</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>44873</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45552</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>44977</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>46261</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45481</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45796</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45729</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45799</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45727</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>45740</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45735</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45727</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45728</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45728</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45494</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45730</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>45803</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46308</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>46266</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45804</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45805</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         <v>45804</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50789,7 +50789,7 @@
         <v>46300</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45810</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45273</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>45617</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>45198</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>46308</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>45810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>46268</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>45812</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51451,7 +51451,7 @@
         <v>45812</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45813</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46310</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>45811</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51743,7 +51743,7 @@
         <v>45813</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>46267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>46267</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45198</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>45819</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>45748</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45753</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45820</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>46310</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>45825</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>45825</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45825</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45825</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52697,7 +52697,7 @@
         <v>45831</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52770,7 +52770,7 @@
         <v>45831</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45831</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52916,7 +52916,7 @@
         <v>45831</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45796</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>45754</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53135,7 +53135,7 @@
         <v>45863</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>44721</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>44712</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>44712</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>44739</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>45849</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>44908</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>45175</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>45395</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45395</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>45721</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>44970</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54016,7 +54016,7 @@
         <v>44812</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45189</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45498</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>45665</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54308,7 +54308,7 @@
         <v>44712</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54381,7 +54381,7 @@
         <v>45722</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>44958</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54527,7 +54527,7 @@
         <v>45395</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45518</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54673,7 +54673,7 @@
         <v>45301</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54746,7 +54746,7 @@
         <v>45873</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44496</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45873</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45465</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45465</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45607</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45611</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>44958</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55330,7 +55330,7 @@
         <v>45465</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55403,7 +55403,7 @@
         <v>45465</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45465</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45395</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>44810</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45077</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45245</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45876</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45876</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>45880</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45880</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45882</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>45882</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56279,7 +56279,7 @@
         <v>45685</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>45673</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56498,7 +56498,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>44711</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56644,7 +56644,7 @@
         <v>45422</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>44711</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45422</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56863,7 +56863,7 @@
         <v>44711</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>44711</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>44805</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>45422</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>45432</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>45720</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45957</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>45985</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46006</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>46041</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>46037</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>46041</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>46051</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58031,7 +58031,7 @@
         <v>46052</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46052</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46062</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58250,7 +58250,7 @@
         <v>46062</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46071</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>46092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>46098</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58542,7 +58542,7 @@
         <v>46110</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58615,7 +58615,7 @@
         <v>46110</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>46114</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>46290</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46100</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45770</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45509</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45400</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>44530</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45629</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>44760</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>44748</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45699</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>46003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45728</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44965</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45365</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45425</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45699</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44711</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45422</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44563</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44753</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44502</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44840</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45110</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45706</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44791</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45322</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45324</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44818</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45159</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45590</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45350</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45511</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45182</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44739</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>45561</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45385</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45364</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45901</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44866</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45902</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45900</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45790</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45595</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45462</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>45912</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45912</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45097</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45838</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45916</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45918</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45008</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45924</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45717</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45009</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45922</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45931</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45931</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45931</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45931</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45875</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45931</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45931</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45931</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45933</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45933</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44949</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45933</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45933</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44880</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45939</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>46174</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>46174</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45427</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45093</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45558</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45945</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45418</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45950</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46181</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>46181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45709</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45952</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45223</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45770</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45385</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45675</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45764</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45960</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44776</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45959</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45959</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45961</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45961</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45963</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45726</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45964</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45100</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45726</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>46190</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45191</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45187</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45930</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46190</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45352</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45967</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45320</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46195</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45968</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45968</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46193</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46195</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46195</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45509</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45973</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45973</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45973</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45973</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45709</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45709</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45978</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45978</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45468</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45118</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45364</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45978</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>44931</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44812</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44624</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45635</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45982</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>46205</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46205</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45985</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45562</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44588</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45989</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45682</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45212</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45672</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45993</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45603</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44945</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46216</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45484</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45777</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46008</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46230</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45784</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45365</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45784</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>46230</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46233</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45624</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46233</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46233</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46232</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45639</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46232</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45637</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46009</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46009</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46009</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46009</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46009</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46237</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46237</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46237</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45678</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>46233</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45488</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45465</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46286</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>46282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>46034</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>46286</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46036</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44873</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>44977</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46036</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45559</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46041</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45481</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>46041</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45792</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>46041</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45796</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45552</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46043</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45729</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45730</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45494</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45727</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45728</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45728</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45727</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45740</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46287</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46049</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45804</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45804</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45135</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45803</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>46051</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46052</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>46051</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45805</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45810</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44615</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>46290</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45617</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45273</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45810</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45811</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45812</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45813</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45813</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>46065</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45753</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45748</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>46069</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46069</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45198</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45497</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>46250</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45820</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46073</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46079</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46079</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45825</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45825</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45825</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45825</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46251</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46083</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46083</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46080</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45831</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45831</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45733</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45831</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45735</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46085</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>46086</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45515</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45607</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45637</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46257</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>46009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46174</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46254</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46098</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46254</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>46297</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44923</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>46104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44519</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45235</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44853</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46104</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46107</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46107</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46105</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46301</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>46301</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46301</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46108</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46111</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46301</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45796</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45754</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44523</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45530</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46261</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45488</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45863</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46303</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44721</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45465</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45465</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45722</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46303</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45465</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45611</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45849</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45395</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45395</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44970</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45465</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45465</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45498</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45721</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44739</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44496</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44908</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45245</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45189</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45395</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45395</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45873</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44810</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44712</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44712</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44712</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>44958</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45665</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44812</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45301</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45876</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>46300</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44563</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45880</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>46308</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45882</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45882</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44896</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45882</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45882</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45545</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45282</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44516</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45818</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45092</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>46308</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44551</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>45358</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>44935</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46267</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45804</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45517</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>46310</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>46310</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44938</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46266</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>45258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46267</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44662</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45888</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45555</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>44501</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>46314</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>46314</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45818</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>44896</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45345</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>46314</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46316</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45937</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45930</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44951</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45488</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45880</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45783</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>44607</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45852</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45011</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45630</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46272</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45155</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45246</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45642</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46274</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45882</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44943</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45191</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>44578</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45498</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45447</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44926</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44748</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44986</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46153</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45320</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45599</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45735</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>44749</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46056</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45112</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45594</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45817</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45425</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>46156</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46156</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45678</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46156</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45355</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46156</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45348</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45579</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45117</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45629</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45042</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45603</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45611</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45588</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45588</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>44867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44853</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>44497</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45026</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45706</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45706</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44498</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45084</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45000</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45027</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45167</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44974</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45096</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45615</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45712</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45163</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45113</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>44729</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45645</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45119</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>45008</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45680</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45545</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45475</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>44926</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>44757</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44817</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45730</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>44711</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45716</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>44894</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45358</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>45273</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>45155</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45509</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>44840</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45414</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45231</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45771</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45251</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45534</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45534</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45264</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45520</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45425</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44501</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>44501</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>44896</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44867</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45211</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>44651</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>44802</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45573</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45349</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>44896</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45222</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>44917</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45337</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45495</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45316</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>44971</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>44971</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45758</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44974</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45250</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45084</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>44551</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44553</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44910</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45559</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45104</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45062</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45337</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45545</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>44860</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45167</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>45482</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>45478</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45615</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>45666</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45596</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45365</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>44558</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>45390</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>45702</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>44496</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45177</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>44581</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45544</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>45484</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45585</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45509</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45089</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45204</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45054</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45204</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45629</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45678</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45719</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45719</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>44578</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45503</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45328</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>45189</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45545</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>44606</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45730</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45169</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>44594</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45100</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45614</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>45231</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45404</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45404</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45607</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45675</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45708</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45244</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45702</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45624</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>44657</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45511</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45259</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45698</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45211</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>44735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>44776</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>44711</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45176</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54054,7 +54054,7 @@
         <v>45581</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45212</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>44903</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>45235</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45735</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45159</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>44909</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>44739</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>44820</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>45315</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45317</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45190</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45357</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45264</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45250</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45163</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45176</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45366</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>44923</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45125</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45264</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>44971</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>44588</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>44952</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>45764</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45637</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56045,7 +56045,7 @@
         <v>45282</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>44803</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>44915</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>44711</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>44711</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45685</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45673</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45422</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45422</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>44805</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45422</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>45432</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45720</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45957</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45985</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46006</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>46037</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46041</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46041</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46052</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46052</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>46051</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>46062</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46062</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>46071</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>46092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>46098</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>46110</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>46110</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58678,7 +58678,7 @@
         <v>46114</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46290</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -601,7 +601,7 @@
         <v>45931</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45804</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45422</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46100</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45770</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>45509</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45400</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>45798</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>45993</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>44530</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44802</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44802</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>45629</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>44760</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>44748</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45699</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>46003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45728</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44965</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45365</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45425</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45699</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44711</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>45687</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45422</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45422</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45712</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>44575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44648</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>44866</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44802</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44802</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>44507</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44817</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44691</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>44767</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44845</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44495</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>44495</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44873</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44544</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44809</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44614</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44855</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>44840</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>44638</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44735</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44563</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44606</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44753</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44606</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44550</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44502</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44977</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44840</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44544</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44550</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45702</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45110</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>45706</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44791</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45322</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45324</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>45889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44818</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>45884</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>45838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>45161</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45159</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45590</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45350</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45511</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45182</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>44739</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>45561</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45385</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45364</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45901</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44866</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45884</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45902</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45900</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45790</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45595</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45211</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45462</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>45908</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45905</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45911</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>45912</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45912</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>45097</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45882</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45838</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45916</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45918</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45918</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45008</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45924</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45717</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45009</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45922</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45931</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45931</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45931</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45931</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46170</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45875</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45931</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45931</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45931</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>44749</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45933</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>46174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45933</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44949</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45933</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45933</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44880</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45939</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>46174</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>46174</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45427</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44952</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45093</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45558</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45945</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45945</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45418</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44551</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45950</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46181</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44931</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44931</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>46181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45709</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45735</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45952</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45223</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45770</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45385</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45675</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45958</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45958</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45958</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45764</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45960</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44776</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45959</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45959</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45961</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45961</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45963</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45726</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45964</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45100</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46188</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45726</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>46190</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45191</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45190</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45187</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45930</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46190</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45352</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45967</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45320</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46195</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45968</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45968</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>46193</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46195</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46195</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46195</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45509</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45973</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45973</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45973</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45973</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45973</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45709</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45709</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45975</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45978</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45978</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45266</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>45468</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>45118</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45978</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45364</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45978</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>44931</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44812</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44624</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45635</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45982</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>46205</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>46205</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45985</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45562</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44588</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45989</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45682</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45212</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45672</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45993</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45603</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44945</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>46216</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45484</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45777</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>46008</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>46008</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>46230</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45784</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45365</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45784</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>46230</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>46233</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45624</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46233</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46233</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>46232</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45639</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>46232</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45637</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>46009</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46009</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46009</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46009</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46009</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46009</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>46009</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46009</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46237</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46237</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46237</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>46237</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45511</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45678</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>46233</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45488</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45465</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46286</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>46282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>46034</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>46286</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46036</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44873</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>44977</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46036</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45559</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46041</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45481</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>46041</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45792</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>46041</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45796</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45552</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46043</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>45729</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45730</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45494</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>45727</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45728</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45728</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45727</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46043</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45740</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46240</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45799</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46287</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>46049</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45804</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45804</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45135</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45803</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>46051</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>46290</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>46052</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>46051</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>45805</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>45810</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44615</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>46290</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45617</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45273</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45810</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45811</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45812</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45812</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45813</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45813</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>46065</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45753</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45748</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>46069</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46069</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>45198</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45497</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>46250</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45819</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45820</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>46073</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>46079</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46079</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45825</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45825</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45825</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45825</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46251</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46083</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>46083</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46080</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45831</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45831</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45733</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45831</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45735</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46085</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>46086</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45515</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45607</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45637</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46257</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>46009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>46174</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>46174</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>46254</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>46098</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32895,7 +32895,7 @@
         <v>46254</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>46297</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44923</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>44893</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45273</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>46104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>44519</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45235</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44853</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>46104</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>46107</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46107</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46105</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46301</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33995,7 +33995,7 @@
         <v>46301</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46301</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>46108</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>46111</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>46301</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34360,7 +34360,7 @@
         <v>45796</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45754</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>44523</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45530</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46261</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45488</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45863</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>46303</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44721</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45465</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45465</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45518</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45722</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>46303</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45465</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45611</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45849</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45607</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45395</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45395</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>44970</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45465</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45465</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45498</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45721</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>45077</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>44739</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44496</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44908</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45245</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45189</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45395</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45395</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45873</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45175</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44810</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44712</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44712</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>44712</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>44958</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45665</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>44812</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45301</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>45876</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>46300</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>44563</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45880</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>46308</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45882</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45882</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>44896</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45882</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45882</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45545</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45282</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>44516</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45818</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45092</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>46308</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44551</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>45358</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>44935</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46267</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45804</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45517</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>46310</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         <v>46310</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44938</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46268</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46266</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>45258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>46267</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44662</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45888</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45555</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>44501</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>46314</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>46314</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45818</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>44896</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45345</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>46314</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46316</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45937</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45930</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>44951</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45488</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45880</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45783</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>44607</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45852</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45011</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45630</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46272</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         <v>45155</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41612,7 +41612,7 @@
         <v>45246</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         <v>45642</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>46274</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>46275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>45882</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44943</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45191</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>44578</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45498</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45447</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44926</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44748</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44986</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46153</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46153</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45320</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45599</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45735</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>44749</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>46056</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45112</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>45594</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45817</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45425</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>46156</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>46156</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45678</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46156</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>45355</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46156</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45348</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45579</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45117</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45629</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45042</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45603</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45611</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45588</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45588</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>44867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44853</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>44497</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45026</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45706</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45706</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44498</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45084</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45000</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45027</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45167</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44974</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45096</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45615</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45712</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45163</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45113</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>44729</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45645</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45119</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>45008</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45680</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45545</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45475</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>44926</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>44757</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>44817</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45730</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>44711</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>45716</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>44894</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>45358</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>45273</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>45155</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45509</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>44840</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>45414</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45231</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45771</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45251</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45534</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45534</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45264</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45520</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45425</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44501</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>44501</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>44896</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44867</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45211</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>44651</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>44802</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45573</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45349</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>44896</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45222</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>44917</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45337</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45495</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45316</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>44971</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>44971</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45758</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>44974</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45250</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45084</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>44551</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44553</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44910</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45559</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45104</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45062</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45337</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45545</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>44860</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45167</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>45482</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>45478</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45615</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>45666</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45596</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45365</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>44558</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>45390</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>45702</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>44496</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45177</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>44581</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>45544</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51109,7 +51109,7 @@
         <v>45484</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45585</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45509</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45089</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45204</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45054</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45204</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45629</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51703,7 +51703,7 @@
         <v>45678</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45719</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45719</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51922,7 +51922,7 @@
         <v>44578</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45503</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45328</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>45189</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52214,7 +52214,7 @@
         <v>45545</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>44606</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52360,7 +52360,7 @@
         <v>45730</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52433,7 +52433,7 @@
         <v>45169</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>44594</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45100</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45614</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52725,7 +52725,7 @@
         <v>45231</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45404</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>45404</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>45607</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45675</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45708</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>45244</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>45702</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45624</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>44657</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45511</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45259</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45698</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45211</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>44735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>44776</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>44711</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45176</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54054,7 +54054,7 @@
         <v>45581</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54127,7 +54127,7 @@
         <v>45212</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>44903</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>45235</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>45735</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>45159</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>44909</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>44739</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>44820</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>45315</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45317</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>45190</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45357</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45264</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>45250</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45163</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45176</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55383,7 +55383,7 @@
         <v>45366</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>44923</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45125</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45264</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>44971</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>44588</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>44952</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -55899,7 +55899,7 @@
         <v>45764</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -55972,7 +55972,7 @@
         <v>45637</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56045,7 +56045,7 @@
         <v>45282</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>44803</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>44915</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>44711</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>44711</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>44711</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>44711</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>44711</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45685</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45673</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45422</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45422</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45422</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>44805</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45422</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>45432</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45720</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45957</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45985</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46006</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>46037</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>46041</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46041</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>46048</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>46051</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46052</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>46052</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>46051</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>46062</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>46062</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>46071</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>46092</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>46098</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>46110</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>46110</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58678,7 +58678,7 @@
         <v>46114</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46290</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
